--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,14 +508,14 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>仅卖出未平仓 700股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -859,14 +859,14 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 700股</t>
         </is>
       </c>
     </row>
@@ -980,92 +980,92 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>688041</v>
+        <v>688062</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>迈威生物</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>688062</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>迈威生物</t>
+          <t>深科技</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>988</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>深科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨年持有底仓）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>988</v>
+        <v>2222</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1082,71 +1082,71 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2222</v>
+        <v>2594</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 600股</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2594</v>
+        <v>300054</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仍买入未平仓 600股</t>
+          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>300054</v>
+        <v>300274</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1156,55 +1156,55 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>300274</v>
+        <v>300308</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>300308</v>
+        <v>300548</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1217,21 +1217,21 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅买入未平仓 600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>300548</v>
+        <v>688008</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,21 +1244,21 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨年持有底仓）</t>
+          <t>仅买入未平仓 500股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>688008</v>
+        <v>688676</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1271,59 +1271,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仅买入未平仓 200股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>688676</v>
+        <v>688778</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>厦钨新能</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
-        <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>688778</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>厦钨新能</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>400</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
         <is>
           <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -751,14 +751,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>；仍卖出未平仓 300股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,14 +751,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 300股</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -980,11 +980,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>688062</v>
+        <v>688041</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>迈威生物</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -994,78 +994,78 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>4000</v>
+        <v>200</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>688062</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>深科技</t>
+          <t>迈威生物</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨年持有底仓）</t>
+          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>988</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>深科技</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2222</v>
+        <v>988</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1082,71 +1082,71 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2594</v>
+        <v>2222</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仍买入未平仓 600股</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>300054</v>
+        <v>2594</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 600股</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>300274</v>
+        <v>300054</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1156,55 +1156,55 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>300308</v>
+        <v>300274</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>300548</v>
+        <v>300308</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1217,21 +1217,21 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨年持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>688008</v>
+        <v>300548</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,21 +1244,21 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨年持有底仓）</t>
+          <t>仅买入未平仓 600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>688676</v>
+        <v>688008</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1271,32 +1271,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+          <t>仅买入未平仓 500股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
+        <v>688676</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>金盘科技</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>200</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>688778</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>厦钨新能</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
         <v>400</v>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -643,14 +643,14 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 40股</t>
+          <t>仅卖出未平仓 140股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -697,14 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 340股</t>
+          <t>仅卖出未平仓 440股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨年持有底仓）</t>
+          <t>仅买入未平仓 500股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨年持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -697,14 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>440</v>
+        <v>340</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 440股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 340股</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -697,14 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>340</v>
+        <v>140</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 340股</t>
+          <t>；仍卖出未平仓 140股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,20 +1096,20 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>
@@ -1285,20 +1285,20 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
         <v>200</v>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
@@ -1326,6 +1326,33 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>603920</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>世运电路</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>500</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -697,14 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 140股</t>
+          <t>；仍卖出未平仓 240股</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>；仍卖出未平仓 1000股</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仍买入未平仓 600股</t>
+          <t>仍买入未平仓 700股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,14 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>240</v>
+        <v>340</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 240股</t>
+          <t>；仍卖出未平仓 340股</t>
         </is>
       </c>
     </row>
@@ -1196,15 +1196,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>300308</v>
+        <v>300548</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1217,21 +1217,21 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仍买入未平仓 400股</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>300548</v>
+        <v>688008</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,44 +1244,44 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨年持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>688008</v>
+        <v>688676</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>688676</v>
+        <v>688778</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>厦钨新能</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1291,24 +1291,24 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>688778</v>
+        <v>603920</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>世运电路</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1318,39 +1318,12 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
-        <is>
-          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>603920</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>世运电路</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>500</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
         <is>
           <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,14 +535,14 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -643,14 +643,14 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 140股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 240股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -697,14 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>340</v>
+        <v>540</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 340股</t>
+          <t>；仍卖出未平仓 540股</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仍买入未平仓 700股</t>
+          <t>仍买入未平仓 1400股</t>
         </is>
       </c>
     </row>
@@ -1196,42 +1196,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>300548</v>
+        <v>300308</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>仍买入未平仓 400股</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>688008</v>
+        <v>300548</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,44 +1244,44 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>688676</v>
+        <v>688008</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>688778</v>
+        <v>688676</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1291,39 +1291,66 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
+        <v>688778</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>厦钨新能</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>400</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>603920</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>世运电路</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
         <v>500</v>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仍买入未平仓 700股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -508,14 +508,14 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 700股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 900股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -751,14 +751,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>；仍卖出未平仓 500股</t>
         </is>
       </c>
     </row>
@@ -1075,14 +1075,14 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 700股</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
@@ -1318,14 +1318,14 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 700股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1356,60 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>512760</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 10000股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>561980</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>芯片设备</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 15000股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+          <t>仅买入未平仓 400股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -562,14 +562,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 2000股</t>
+          <t>；仍卖出未平仓 1500股</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1000股</t>
+          <t>；仍卖出未平仓 800股</t>
         </is>
       </c>
     </row>
@@ -1156,14 +1156,14 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>仅买入未平仓 10000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 15000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15000</v>
+        <v>22000</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 15000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 22000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨年持有底仓）</t>
+          <t>仅买入未平仓 500股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -805,14 +805,14 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 800股</t>
+          <t>；仍卖出未平仓 1000股</t>
         </is>
       </c>
     </row>
@@ -1258,20 +1258,20 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>100</v>
       </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -859,14 +859,14 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 700股</t>
+          <t>；仍卖出未平仓 500股</t>
         </is>
       </c>
     </row>
@@ -1258,20 +1258,20 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22000</v>
+        <v>24000</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 22000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 24000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -1075,14 +1075,14 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>仅买入未平仓 15000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 18000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>24000</v>
+        <v>28000</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 24000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 28000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 500股（跨年持有底仓）</t>
+          <t>仅买入未平仓 700股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 900股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -799,20 +799,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 800股（跨年持有底仓）</t>
+          <t>仅买入未平仓 1200股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -859,14 +859,14 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 500股</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -994,14 +994,14 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1000股</t>
+          <t>；仍卖出未平仓 800股</t>
         </is>
       </c>
     </row>
@@ -1075,14 +1075,14 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仍买入未平仓 1400股</t>
+          <t>仍买入未平仓 1600股</t>
         </is>
       </c>
     </row>
@@ -1156,14 +1156,14 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>仅买入未平仓 18000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 20000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>28000</v>
+        <v>40000</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 28000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 40000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -562,14 +562,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1500股</t>
+          <t>；仍卖出未平仓 1400股</t>
         </is>
       </c>
     </row>
@@ -751,14 +751,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 500股</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1200股（跨年持有底仓）</t>
+          <t>仅买入未平仓 1300股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仍买入未平仓 1600股</t>
+          <t>仍买入未平仓 1400股</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仍买入未平仓 200股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>仅买入未平仓 20000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 27000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 40000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 50000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1300股（跨年持有底仓）</t>
+          <t>仅买入未平仓 1500股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1400</v>
+        <v>1700</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仍买入未平仓 1400股</t>
+          <t>仍买入未平仓 1700股</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仍买入未平仓 500股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 700股（跨年持有底仓）</t>
+          <t>仅买入未平仓 900股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -575,11 +575,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2837</v>
+        <v>123269</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>金杨转债</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -589,24 +589,24 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 100股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 10股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123269</v>
+        <v>300394</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金杨转债</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -616,24 +616,24 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 10股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 240股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>300394</v>
+        <v>300450</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -643,24 +643,24 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 240股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 700股</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>300450</v>
+        <v>300502</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -670,24 +670,24 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>700</v>
+        <v>540</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 700股</t>
+          <t>；仍卖出未平仓 540股</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>300502</v>
+        <v>300660</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>江苏雷利</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -697,24 +697,24 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 540股</t>
+          <t>仅卖出未平仓 1000股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300660</v>
+        <v>300750</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>江苏雷利</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -724,24 +724,24 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 1000股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300750</v>
+        <v>512000</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>券商ETF</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -751,55 +751,55 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>400</v>
+        <v>20000</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>仅卖出未平仓 20000股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>512000</v>
+        <v>600259</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>券商ETF</t>
+          <t>中稀有色</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 20000股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>600259</v>
+        <v>600498</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中稀有色</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -812,44 +812,44 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅买入未平仓 1600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>600498</v>
+        <v>601208</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1500股（跨年持有底仓）</t>
+          <t>；仍卖出未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>601208</v>
+        <v>601899</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -859,24 +859,24 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>；仍卖出未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>601899</v>
+        <v>603881</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -893,48 +893,48 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 300股</t>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>603881</v>
+        <v>688025</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 200股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>688025</v>
+        <v>688035</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -947,44 +947,44 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+          <t>仅买入未平仓 400股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>688035</v>
+        <v>688041</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨年持有底仓）</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>688041</v>
+        <v>688062</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>迈威生物</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -994,109 +994,109 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 800股</t>
+          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>688062</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>迈威生物</t>
+          <t>深科技</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>988</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>深科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨年持有底仓）</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>988</v>
+        <v>2222</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2222</v>
+        <v>2594</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>300</v>
+        <v>1600</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1109,44 +1109,44 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仍买入未平仓 1600股</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2594</v>
+        <v>300054</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仍买入未平仓 1700股</t>
+          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>300054</v>
+        <v>300274</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1156,24 +1156,24 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>300274</v>
+        <v>300308</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1183,55 +1183,55 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>300308</v>
+        <v>300548</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>300548</v>
+        <v>688008</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,44 +1244,44 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仍买入未平仓 700股</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>688008</v>
+        <v>688676</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 500股</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>688676</v>
+        <v>688778</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>厦钨新能</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1291,24 +1291,24 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仅卖出未平仓 700股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>688778</v>
+        <v>603920</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>世运电路</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1318,55 +1318,55 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 700股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>603920</v>
+        <v>512760</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>世运电路</t>
+          <t>芯片ETF</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
+          <t>仅买入未平仓 37000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>512760</v>
+        <v>561980</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>芯片设备</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>27000</v>
+        <v>56000</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1379,34 +1379,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>仅买入未平仓 27000股（跨年持有底仓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>561980</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>芯片设备</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>仅买入未平仓 50000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 56000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 900股（跨年持有底仓）</t>
+          <t>仅买入未平仓 1000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 700股</t>
         </is>
       </c>
     </row>
@@ -575,38 +575,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123269</v>
+        <v>2837</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金杨转债</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 10股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>300394</v>
+        <v>123269</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>金杨转债</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -616,24 +616,24 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 240股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 10股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>300450</v>
+        <v>300394</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -643,24 +643,24 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 700股</t>
+          <t>仅卖出未平仓 240股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>300502</v>
+        <v>300450</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -670,24 +670,24 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 540股</t>
+          <t>；仍卖出未平仓 700股</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>300660</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>江苏雷利</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -697,24 +697,24 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 1000股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 540股</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300750</v>
+        <v>300660</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>江苏雷利</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -724,24 +724,24 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>仅卖出未平仓 1000股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>512000</v>
+        <v>300750</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>券商ETF</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -751,55 +751,55 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>20000</v>
+        <v>400</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 20000股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>600259</v>
+        <v>512000</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中稀有色</t>
+          <t>券商ETF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仅卖出未平仓 20000股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>600498</v>
+        <v>600259</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>中稀有色</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -812,44 +812,44 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1600股（跨年持有底仓）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>601208</v>
+        <v>600498</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 300股</t>
+          <t>仅买入未平仓 1600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>601899</v>
+        <v>601208</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -859,24 +859,24 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 300股</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>603881</v>
+        <v>601899</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -893,48 +893,48 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>688025</v>
+        <v>603881</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>杰普特</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>仅买入未平仓 200股（跨年持有底仓）</t>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>688035</v>
+        <v>688025</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>德邦科技</t>
+          <t>杰普特</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -947,44 +947,44 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>仅买入未平仓 400股（跨年持有底仓）</t>
+          <t>仅买入未平仓 200股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>688041</v>
+        <v>688035</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>德邦科技</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>仅买入未平仓 400股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>688062</v>
+        <v>688041</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>迈威生物</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -994,109 +994,109 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>4000</v>
+        <v>600</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>688062</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>深科技</t>
+          <t>迈威生物</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>仅买入未平仓 600股（跨年持有底仓）</t>
+          <t>仅卖出未平仓 4000股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>988</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>深科技</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>仅买入未平仓 600股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2222</v>
+        <v>988</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2594</v>
+        <v>2222</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1600</v>
+        <v>300</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1109,44 +1109,44 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仍买入未平仓 1600股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>300054</v>
+        <v>2594</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>鼎龙股份</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 1600股</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>300274</v>
+        <v>300054</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>阳光电源</t>
+          <t>鼎龙股份</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1156,24 +1156,24 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>300308</v>
+        <v>300274</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>阳光电源</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1183,55 +1183,55 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 100股</t>
+          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>300548</v>
+        <v>300308</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>；仍卖出未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>688008</v>
+        <v>300548</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>长芯博创</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1244,44 +1244,44 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>仍买入未平仓 700股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>688676</v>
+        <v>688008</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>仍买入未平仓 900股</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>688778</v>
+        <v>688676</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1291,24 +1291,24 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 700股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>603920</v>
+        <v>688778</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>世运电路</t>
+          <t>厦钨新能</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1318,66 +1318,93 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 700股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>512760</v>
+        <v>603920</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>芯片ETF</t>
+          <t>世运电路</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>仅买入未平仓 37000股（跨年持有底仓）</t>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>512760</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>芯片ETF</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>37000</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>仅买入未平仓 37000股（跨年持有底仓）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
         <v>561980</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>芯片设备</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C36" t="n">
         <v>56000</v>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>仅买入未平仓 56000股（跨年持有底仓）</t>
         </is>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -478,7 +478,7 @@
         <v>1000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>58329</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -511,7 +511,7 @@
         <v>700</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>46042.79</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -538,7 +538,7 @@
         <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>38262</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         <v>1400</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>55182.29</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>6626</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -619,7 +619,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1616.66</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
         <v>240</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>70175.28</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>700</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>30215.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>540</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>287104.93</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>1000</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>36625</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         <v>400</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>150218.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>20000</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>10180</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>7026.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>1600</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>84665.92</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>200</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>11711.32</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>300</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>8469</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>300</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>12726</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>200</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>79354.55</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>400</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>35694.66</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -997,7 +997,7 @@
         <v>600</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>189680.31</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>4000</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>127885</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>600</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>25838.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1078,7 +1078,7 @@
         <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>15396</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>300</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>18075.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1126,7 +1126,7 @@
         <v>1600</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>146110.36</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>800</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>73412</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>200</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>31750</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>102676.67</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>300</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>85787</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1261,7 +1261,7 @@
         <v>900</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>196148.98</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>200</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>13394</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>700</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>38143</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>500</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>16355</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>37000</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>41028.71</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
         <v>56000</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>39415.24</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="D2" t="n">
-        <v>58329</v>
+        <v>64052</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 1100股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="D31" t="n">
-        <v>196148.98</v>
+        <v>235349.69</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 900股</t>
+          <t>仍买入未平仓 1100股</t>
         </is>
       </c>
     </row>
@@ -1318,14 +1318,14 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="F33" t="n">
-        <v>38143</v>
+        <v>61338</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 700股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 1200股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37000</v>
+        <v>40000</v>
       </c>
       <c r="D35" t="n">
-        <v>41028.71</v>
+        <v>44226.71</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>仅买入未平仓 37000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 40000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>56000</v>
+        <v>60000</v>
       </c>
       <c r="D36" t="n">
-        <v>39415.24</v>
+        <v>42063.24</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 56000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 60000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D2" t="n">
-        <v>64052</v>
+        <v>69675</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1100股（跨年持有底仓）</t>
+          <t>仅买入未平仓 1200股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -562,14 +562,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="F5" t="n">
-        <v>55182.29</v>
+        <v>47299.11</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1400股</t>
+          <t>；仍卖出未平仓 1200股</t>
         </is>
       </c>
     </row>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>6626</v>
+        <v>19580.25</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,7 +596,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D25" t="n">
-        <v>18075.5</v>
+        <v>24350.29</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仍买入未平仓 400股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -562,14 +562,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F5" t="n">
-        <v>47299.11</v>
+        <v>55182.29</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1200股</t>
+          <t>；仍卖出未平仓 1400股</t>
         </is>
       </c>
     </row>
@@ -859,14 +859,14 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F16" t="n">
-        <v>11711.32</v>
+        <v>17566.98</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>；仍卖出未平仓 300股</t>
         </is>
       </c>
     </row>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D25" t="n">
-        <v>24350.29</v>
+        <v>18075.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仍买入未平仓 400股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="D31" t="n">
-        <v>235349.69</v>
+        <v>114123.66</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 1100股</t>
+          <t>仍买入未平仓 500股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -475,10 +475,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="D2" t="n">
-        <v>69675</v>
+        <v>75201</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1200股（跨年持有底仓）</t>
+          <t>仅买入未平仓 1300股（跨年持有底仓）</t>
         </is>
       </c>
     </row>
@@ -562,14 +562,14 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F5" t="n">
-        <v>55182.29</v>
+        <v>58982.58</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 1400股</t>
+          <t>；仍卖出未平仓 1500股</t>
         </is>
       </c>
     </row>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="D6" t="n">
-        <v>19580.25</v>
+        <v>32315</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -596,7 +596,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仍买入未平仓 500股</t>
         </is>
       </c>
     </row>
@@ -859,14 +859,14 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F16" t="n">
-        <v>17566.98</v>
+        <v>11711.32</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 300股</t>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D25" t="n">
-        <v>18075.5</v>
+        <v>24416.86</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仍买入未平仓 400股</t>
         </is>
       </c>
     </row>
@@ -1156,14 +1156,14 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F27" t="n">
-        <v>73412</v>
+        <v>55059</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 800股（平旧仓，无对应买入）</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="D31" t="n">
-        <v>114123.66</v>
+        <v>155160.8</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>仍买入未平仓 500股</t>
+          <t>仍买入未平仓 700股</t>
         </is>
       </c>
     </row>
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="D36" t="n">
-        <v>42063.24</v>
+        <v>48633.24</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>仅买入未平仓 60000股（跨年持有底仓）</t>
+          <t>仅买入未平仓 70000股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="D15" t="n">
-        <v>84665.92</v>
+        <v>92865.92</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>仅买入未平仓 1600股（跨年持有底仓）</t>
+          <t>仅买入未平仓 1800股（跨年持有底仓）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026年度.xlsx
+++ b/reports/剩余持仓_2026年度.xlsx
@@ -859,14 +859,14 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F16" t="n">
-        <v>11711.32</v>
+        <v>17566.98</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>；仍卖出未平仓 300股</t>
         </is>
       </c>
     </row>
@@ -1156,14 +1156,14 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F27" t="n">
-        <v>55059</v>
+        <v>36706</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 600股</t>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>
